--- a/artfynd/A 21986-2023 artfynd.xlsx
+++ b/artfynd/A 21986-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61714656</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753637</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081097</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554191</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554193</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1869,6 +1919,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554197</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1999,6 +2054,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554198</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2129,6 +2189,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554199</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2259,6 +2324,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2384,6 +2454,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474080</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2509,6 +2584,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474107</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2634,6 +2714,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474108</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2759,6 +2844,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474476</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2884,6 +2974,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474477</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3009,6 +3104,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474478</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3134,6 +3234,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474479</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3259,6 +3364,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474481</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3384,6 +3494,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474482</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3509,6 +3624,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768262</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3634,6 +3754,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768264</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3759,6 +3884,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768265</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3884,6 +4014,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768266</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4009,6 +4144,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768267</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4139,6 +4279,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834335</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4269,6 +4414,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834337</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4399,6 +4549,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834339</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4529,6 +4684,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834340</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4659,6 +4819,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753089</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4789,6 +4954,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753090</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4919,6 +5089,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753092</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5049,6 +5224,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93753093</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5179,6 +5359,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5309,6 +5494,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080375</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5439,6 +5629,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080376</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5569,6 +5764,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080378</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5699,6 +5899,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080384</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5829,6 +6034,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080386</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5959,6 +6169,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080387</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6089,6 +6304,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555035</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6219,6 +6439,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555037</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6349,6 +6574,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555039</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6479,6 +6709,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6609,6 +6844,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555090</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6739,6 +6979,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555091</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6869,6 +7114,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555092</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6999,6 +7249,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555093</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7124,6 +7379,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473527</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7254,6 +7514,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766223</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7384,6 +7649,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766224</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7514,6 +7784,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766225</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7644,6 +7919,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766226</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7774,6 +8054,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833112</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7904,6 +8189,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833120</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8034,6 +8324,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833122</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8164,6 +8459,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833123</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8275,6 +8575,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96191167</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8377,8 +8682,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105404720</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>